--- a/artfynd/A 7276-2025 artfynd.xlsx
+++ b/artfynd/A 7276-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6564205</v>
+        <v>80576630</v>
       </c>
       <c r="B2" t="n">
-        <v>105431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>86845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>231677</v>
+        <v>952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mjölfibbla</t>
+          <t>Lundfjällskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hieracium farinaceum</t>
+          <t>Lepiota subalba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Stenstr.) Dahlst.</t>
+          <t>Kühner ex P.D.Orton</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Igelsjö, 750 m SSV om Igelsjö gård, Vg</t>
+          <t>Åbod NV, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>424556.5539140343</v>
+        <v>424560</v>
       </c>
       <c r="R2" t="n">
-        <v>6481110.079202989</v>
+        <v>6481066</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-07-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-07-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,29 +757,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>vägslänt i lövskog</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Anders Bertilsson</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+          <t>Kuperad grandominerad skog med inslag av div. löv. Hassel björk mm</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
+          <t>Börje H Fagerlind</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Bertilsson</t>
+          <t>Börje H Fagerlind</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -801,16 +788,11 @@
         <v>63800262</v>
       </c>
       <c r="B3" t="n">
-        <v>90652</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -838,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>424581.7690250929</v>
+        <v>424582</v>
       </c>
       <c r="R3" t="n">
-        <v>6481085.52375401</v>
+        <v>6481086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +853,9 @@
           <t>2012-09-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-09-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -912,6 +884,553 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>80576623</v>
+      </c>
+      <c r="B4" t="n">
+        <v>86818</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4852</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kastanjefjällskivling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lepiota castanea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Åbod NV, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>424560</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6481066</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lerdala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-10-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-10-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kuperad grandominerad skog med inslag av div. löv. Hassel björk mm</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>80576626</v>
+      </c>
+      <c r="B5" t="n">
+        <v>86811</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4861</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Piggfjällskivling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Echinoderma jacobi</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Vellinga &amp; Knudsen) Gminder</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Åbod NV, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>424560</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6481066</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lerdala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-10-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-10-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kuperad grandominerad skog med inslag av div. löv. Hassel björk mm</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Börje H Fagerlind</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>102930162</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104808</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220464</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lundbräsma</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cardamine impatiens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Åbod NV, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>424619</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6481086</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lerdala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2002-06-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2002-06-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6564205</v>
+      </c>
+      <c r="B7" t="n">
+        <v>108506</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>231677</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mjölfibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hieracium farinaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Stenstr.) Dahlst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Igelsjö, 750 m SSV om Igelsjö gård, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>424557</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6481110</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lerdala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2005-07-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2005-07-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>vägslänt i lövskog</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6565551</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108865</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>231710</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pilfibbla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hieracium hepaticolor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Stenstr.) Johanss. &amp; Sam.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Igelsjö, 750 m SSV om Igelsjö gård, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>424567</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6481110</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lerdala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2007-06-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2007-06-14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Även belägg i eget herbarium</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>vägslänt i lövskog</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Biologiska Museet, Lunds Universitet</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
